--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הילה רוח – זאת השנה שלי</v>
+        <v>אופיר הדס – משוגע</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%96%d7%90%d7%aa-%d7%94%d7%a9%d7%a0%d7%94-%d7%a9%d7%9c%d7%99/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%94%d7%93%d7%a1-%d7%9e%d7%a9%d7%95%d7%92%d7%a2/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הילה רוח שרה שיר שנשמע כמו הבטחה לעצמה, לא הכרזה חגיגית אלא ניסיון להאמין.הבלדה המלודית-השקטה מושרת ברכות כמעט מלוחשת היא לא רק אסתטיקה: היא המנגנון הפסיכולוגי של הדוברת. זאת לא צעקה של ביטחון  זאת לחישה של אומץ. "אני יש לי</v>
+        <v>“משוגע” של אופיר הדס הוא שיר עם לב כפול: מצד אחד – טקסט פנימי, כמעט קלסטרופובי, על אדם הסגור בתוך עצמו. מצד שני – עיבוד לטיני קצבי (בין סמבה לרומבה) שמניע את הגוף קדימה. הפער הזה הוא לא מקרי. הוא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הילה רוח – זאת השנה שלי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>בן ארצי ואהרון רזאל – תודה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%95%d7%90%d7%94%d7%a8%d7%95%d7%9f-%d7%a8%d7%96%d7%90%d7%9c-%d7%aa%d7%95%d7%93%d7%94/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>“תודה” הוא שיר הודיה  אבל לא נאיבי.. זו אינה שמחה פשוטה, אלא הודיה שעברה דרך כאב, ספק ושבר. הדואט בין שני קולות שמגיעים מעולמות מעט שונים  – חילוני־פואטי (בן ארצי) ואמוני מובהק (אהרן רזאל) —יוצר מרחב שמחבר בין רוחניות אישית</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>בן ארצי ואהרון רזאל – תודה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>דניאל גרנט – מיס דייזי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%92%d7%a8%d7%a0%d7%98-%d7%9e%d7%99%d7%a1-%d7%93%d7%99%d7%99%d7%96%d7%99/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>זה לא ראפ על הצלחה – זה ראפ על הזמן שבין ההצלחות. השיר של דניאל גרנט עוסק באזור הכי פחות מדובר בקריירה: לא ההתחלה, לא הפריצה, אלא השנים האפורות באמצע, כשהכול כבר כמעט קרה… ואז נעצר. הבית הראשון מציג ביוגרפיה</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>דניאל גרנט – מיס דייזי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>רז פרסטן – ביג</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%96-%d7%a4%d7%a8%d7%a1%d7%98%d7%9f-%d7%91%d7%99%d7%92/</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>"ביג” של רז פרסטן הוא רוק מהיר, מחוספס וכמעט פאנקי-פוסט-פאנק.  הליבה הטקסטואלית נשמעת כהצהרת דור. הוא לא מדבר על הצלחה.  הוא מדבר על התנאים להיות בכלל נשמע. הלהקה מצהירה בדף המידע כי שואבת השראה מלהקת כ-Turnstile ומ –  של Fontaines</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>רז פרסטן – ביג</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נועם קלינשטיין – אותו דבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="C6" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a7%d7%9c%d7%99%d7%a0%d7%a9%d7%98%d7%99%d7%99%d7%9f-%d7%90%d7%95%d7%aa%d7%95-%d7%93%d7%91%d7%a8/</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>נועם קלינשטיין שרה שיר פופ קצבי אולד-סקול עם דרייב של נסיעה (“driving pop”) — כלומר שיר שנשען על גרוב רציף, מרכז הרמוני יציב וקולות ליווי נשיים שעוטפים ולא שוברים את הזרימה. זה לא שיר פרידה קלאסי אלא שיר אחרי הפרידה..</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נועם קלינשטיין – אותו דבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>משה כורסיה – עומד מולך היום</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="C7" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%9b%d7%95%d7%a8%d7%a1%d7%99%d7%94-%d7%a2%d7%95%d7%9e%d7%93-%d7%9e%d7%95%d7%9c%d7%9a-%d7%94%d7%99%d7%95%d7%9d/</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>זהו שיר תפילה במבנה של בלדה מודרנית. לא תפילה ליטורגית, אלא אישית, חשופה, כמעט יומיומית. השיר מתאר אדם שהתעייף מלהחזיק דימוי חזק כלפי חוץ,  ומבקש בפעם הראשונה לא להוכיח, אלא להשתייך. משה כורסיה מספר כי הרקע לשיר – התמודדות עם</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>משה כורסיה – עומד מולך היום</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נתן כהן – ותגיד לי אתה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9f-%d7%9b%d7%94%d7%9f-%d7%95%d7%aa%d7%92%d7%99%d7%93-%d7%9c%d7%99-%d7%90%d7%aa%d7%94/</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v>נתן כהן, שבלט ב"הנשמות הטהורות" ביכולת לכתוב ולהלחין שירים עם פשטות פיוטית ("אחכה לך", "אחרי שהסירות"), ממשיך כאן קו סגנוני מוכר. השיר מדבר על זמן של עייפות תרבותית.על עולם שבו הטבע מתייבש לאט, הילדים משחקים כאילו כלום, האוויר כבד, והמבוגר</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נתן כהן – ותגיד לי אתה</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>נוגה פרידמן – עזרה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%92%d7%94-%d7%a4%d7%a8%d7%99%d7%93%d7%9e%d7%9f-%d7%a2%d7%96%d7%a8%d7%94/</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>"עזרה" ששרה נוגה פרידמן הוא שיר שקשה לנתח אותו מבלי לזכור את נסיבות כתיבתו,  אבל כוחו האמיתי הוא בכך שהוא עומד גם בלי הביוגרפיה. האובדן האישי של בן זוגה, עידו רוזנטל ז"ל, נוכח בשיר, אך הוא לא מתואר. אין אזכור</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>נוגה פרידמן – עזרה</v>
+        <v>אופיר הדס – משוגע</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר הדס – משוגע</v>
+        <v>פטרושקה – גלוחי העורף</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%94%d7%93%d7%a1-%d7%9e%d7%a9%d7%95%d7%92%d7%a2/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%95%d7%a9%d7%a7%d7%94-%d7%92%d7%9c%d7%95%d7%97%d7%99-%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“משוגע” של אופיר הדס הוא שיר עם לב כפול: מצד אחד – טקסט פנימי, כמעט קלסטרופובי, על אדם הסגור בתוך עצמו. מצד שני – עיבוד לטיני קצבי (בין סמבה לרומבה) שמניע את הגוף קדימה. הפער הזה הוא לא מקרי. הוא</v>
+        <v>"גלוחי העורף" של עידו פטרושקה הוא שיר עירוני לא “על העיר” אלא מתוכה.. אין כאן עמדה מוסרית ברורה, אין פתרון, אין סיפור שלם. יש אוסף מבטים קצרים, כמעט תיעודיים, שמרחפים בין חמלה לאדישות. הקול המחוספס והמקצב  הסימטרי יוצרים תחושת הליכה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר הדס – משוגע</v>
+        <v>פטרושקה – גלוחי העורף</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פטרושקה – גלוחי העורף</v>
+        <v>נטע ברזילי – סרנדה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%95%d7%a9%d7%a7%d7%94-%d7%92%d7%9c%d7%95%d7%97%d7%99-%d7%94%d7%a2%d7%95%d7%a8%d7%a3/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%a1%d7%a8%d7%a0%d7%93%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גלוחי העורף" של עידו פטרושקה הוא שיר עירוני לא “על העיר” אלא מתוכה.. אין כאן עמדה מוסרית ברורה, אין פתרון, אין סיפור שלם. יש אוסף מבטים קצרים, כמעט תיעודיים, שמרחפים בין חמלה לאדישות. הקול המחוספס והמקצב  הסימטרי יוצרים תחושת הליכה</v>
+        <v>“סרנדה” ששרה נטע ברזילי היא בלדה אמוציונלית שמצליחה לעשות מהלך עדין מאוד: להישמע כמו שיר אהבה,  אבל בפועל להיות שיר על חוסר אונים בתוך אהבה. שיר של שחיקה איטית שהופך דרמה נואשת. הפער הראשון בשיר הוא פער תקשורתי: "אני יכולה לספור</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פטרושקה – גלוחי העורף</v>
+        <v>נטע ברזילי – סרנדה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – סרנדה</v>
+        <v>ישי ריבו – הנשמה לא meta</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%a1%d7%a8%d7%a0%d7%93%d7%94/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a9%d7%99-%d7%a8%d7%99%d7%91%d7%95-%d7%94%d7%a0%d7%a9%d7%9e%d7%94-%d7%9c%d7%90-meta/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-16</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“סרנדה” ששרה נטע ברזילי היא בלדה אמוציונלית שמצליחה לעשות מהלך עדין מאוד: להישמע כמו שיר אהבה,  אבל בפועל להיות שיר על חוסר אונים בתוך אהבה. שיר של שחיקה איטית שהופך דרמה נואשת. הפער הראשון בשיר הוא פער תקשורתי: "אני יכולה לספור</v>
+        <v>“הנשמה לא Meta” הוא שיר אמוני מובהק  אבל שונה בנוף של ישי ריבו. במקום תפילה ישירה לאל, יש כאן פנייה לנשמה עצמה. במקום אויב רוחני מופשט  האתגר הוא עידן הרשתות. השיר מציב עימות חד: נשמה נצחית מול מציאות דיגיטלית. למה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – סרנדה</v>
+        <v>ישי ריבו – הנשמה לא meta</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ישי ריבו – הנשמה לא meta</v>
+        <v>עלמה גוב – בסיבוב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a9%d7%99-%d7%a8%d7%99%d7%91%d7%95-%d7%94%d7%a0%d7%a9%d7%9e%d7%94-%d7%9c%d7%90-meta/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%9c%d7%9e%d7%94-%d7%92%d7%95%d7%91-%d7%91%d7%a1%d7%99%d7%91%d7%95%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“הנשמה לא Meta” הוא שיר אמוני מובהק  אבל שונה בנוף של ישי ריבו. במקום תפילה ישירה לאל, יש כאן פנייה לנשמה עצמה. במקום אויב רוחני מופשט  האתגר הוא עידן הרשתות. השיר מציב עימות חד: נשמה נצחית מול מציאות דיגיטלית. למה</v>
+        <v>“בסיבוב” ששרה עלמה גוב הוא שיר תנועה פיזית ונפשית. הוא נכתב מתוך מעבר מהמושב לתל אביב, אבל במהותו זה שיר על ניסיון לברוח ועל ההבנה שהלב נוסע יחד איתך.הקצב המהיר והאנרגיה הכמעט כבישית אינם רק תפאורה – הם חלק מהרעיון</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ישי ריבו – הנשמה לא meta</v>
+        <v>עלמה גוב – בסיבוב</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עלמה גוב – בסיבוב</v>
+        <v>נועה קירל – או לה פופה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%9c%d7%9e%d7%94-%d7%92%d7%95%d7%91-%d7%91%d7%a1%d7%99%d7%91%d7%95%d7%91/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%95-%d7%9c%d7%94-%d7%a4%d7%95%d7%a4%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“בסיבוב” ששרה עלמה גוב הוא שיר תנועה פיזית ונפשית. הוא נכתב מתוך מעבר מהמושב לתל אביב, אבל במהותו זה שיר על ניסיון לברוח ועל ההבנה שהלב נוסע יחד איתך.הקצב המהיר והאנרגיה הכמעט כבישית אינם רק תפאורה – הם חלק מהרעיון</v>
+        <v>הביטוי “או לה פופהה” הוא תעתיק עברי של הצרפתית: Oh là là, poupée. פירושו בערך: “אוי-לה-לה, בובה!”. זה נאמר בדרך כלל בטון פלרטטני/מחמיא, כמו לומר למישהי שהיא יפה או מושכת, לפעמים קצת מוגזם או הומוריסטי. נועה קירל שרה פופ עכשווי,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עלמה גוב – בסיבוב</v>
+        <v>נועה קירל – או לה פופה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה קירל – או לה פופה</v>
+        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%90%d7%95-%d7%9c%d7%94-%d7%a4%d7%95%d7%a4%d7%94/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%99%d7%aa%d7%99-%d7%92%d7%9c%d7%95-%d7%9b%d7%aa%d7%95%d7%91-%d7%a2%d7%9c-%d7%94%d7%a7%d7%99%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-18</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הביטוי “או לה פופהה” הוא תעתיק עברי של הצרפתית: Oh là là, poupée. פירושו בערך: “אוי-לה-לה, בובה!”. זה נאמר בדרך כלל בטון פלרטטני/מחמיא, כמו לומר למישהי שהיא יפה או מושכת, לפעמים קצת מוגזם או הומוריסטי. נועה קירל שרה פופ עכשווי,</v>
+        <v>“כתוב על הקיר”  ששר הראל סקעת הוא שיר שנע בין קלאוסטרופוביה להתפרקות משחררת, ומקבל את שיאו בהפיכה לדאנס-טראנס מרקיד בניצוחו הדי־ג’יי איתי גלו. זה  מעבר סגנוני.שמעצים דרמה נפשית שמתרחשת דרך הקצב. הטקסט מתחיל במרחב סגור מאוד. התחושה כמעט דיכאונית – חיים</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה קירל – או לה פופה</v>
+        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
+        <v>פלורה – מנגינה מחייכת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a8%d7%90%d7%9c-%d7%a1%d7%a7%d7%a2%d7%aa-%d7%90%d7%99%d7%aa%d7%99-%d7%92%d7%9c%d7%95-%d7%9b%d7%aa%d7%95%d7%91-%d7%a2%d7%9c-%d7%94%d7%a7%d7%99%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%94-%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94-%d7%9e%d7%97%d7%99%d7%99%d7%9b%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“כתוב על הקיר”  ששר הראל סקעת הוא שיר שנע בין קלאוסטרופוביה להתפרקות משחררת, ומקבל את שיאו בהפיכה לדאנס-טראנס מרקיד בניצוחו הדי־ג’יי איתי גלו. זה  מעבר סגנוני.שמעצים דרמה נפשית שמתרחשת דרך הקצב. הטקסט מתחיל במרחב סגור מאוד. התחושה כמעט דיכאונית – חיים</v>
+        <v>פלורה שרה שיר שמתקיים כמעט כולו במרחב עדין – לא דרמה, לא וידוי גדול, אלא תהליך פנימי. הוא נשמע כמו שיר־מסע, אבל לא מסע גיאוגרפי אלא מעבר פסיכולוגי: ממצב קפוא למצב זורם. בולט בהאזנה ראשונה הפער בין טקסט שמדבר על</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הראל סקעת איתי גלו – כתוב על הקיר</v>
+        <v>פלורה – מנגינה מחייכת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פלורה – מנגינה מחייכת</v>
+        <v>סטטיק – מנדם‎</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%94-%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94-%d7%9e%d7%97%d7%99%d7%99%d7%9b%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%98%d7%99%d7%a7-%d7%9e%d7%a0%d7%93%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>פלורה שרה שיר שמתקיים כמעט כולו במרחב עדין – לא דרמה, לא וידוי גדול, אלא תהליך פנימי. הוא נשמע כמו שיר־מסע, אבל לא מסע גיאוגרפי אלא מעבר פסיכולוגי: ממצב קפוא למצב זורם. בולט בהאזנה ראשונה הפער בין טקסט שמדבר על</v>
+        <v>סטטיק עושה שיר פופ-ראפ שמבוסס על ערבוב תרבויות: עברית  + סלנג לונדוני + היפ-הופ בריטי  והכול עטוף בשאלה אחת: מה קורה לאגו כשפתאום מופיע רגש אמיתי? המילה mandem – חבורת גברים מגדירה קוד גברי של כוח, סטטוס וחסינות רגשית. השיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פלורה – מנגינה מחייכת</v>
+        <v>סטטיק – מנדם‎</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סטטיק – מנדם‎</v>
+        <v>דניאל בן חיים – לבד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%98%d7%98%d7%99%d7%a7-%d7%9e%d7%a0%d7%93%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%91%d7%9f-%d7%97%d7%99%d7%99%d7%9d-%d7%9c%d7%91%d7%93/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>סטטיק עושה שיר פופ-ראפ שמבוסס על ערבוב תרבויות: עברית  + סלנג לונדוני + היפ-הופ בריטי  והכול עטוף בשאלה אחת: מה קורה לאגו כשפתאום מופיע רגש אמיתי? המילה mandem – חבורת גברים מגדירה קוד גברי של כוח, סטטוס וחסינות רגשית. השיר</v>
+        <v>דניאל בן חיים שר שיר של כאב אישי הנובע מהצטברות רגש והופך להתפרצות קולית. השיר לא מתאר אהבה במשבר אלא את החיים אחרי, כשהרגש כבר נגמר בצד השני ונשאר רק בצד אחד. השיר בנוי סביב פעולה חוזרת – “תקחי ממני”.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סטטיק – מנדם‎</v>
+        <v>דניאל בן חיים – לבד</v>
       </c>
     </row>
   </sheetData>
